--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2679,6 +2679,1683 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120237239</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>677002</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6614969</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120237674</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>676920</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6615057</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120237628</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>676920</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6615038</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120237246</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>677001</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6614969</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120236998</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>676961</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6615062</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120237707</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>676938</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6615070</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120237606</v>
+      </c>
+      <c r="B27" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>676929</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6614995</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120237872</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>677009</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6615043</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120238171</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>676863</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6615036</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120237190</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>677006</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6614978</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120236816</v>
+      </c>
+      <c r="B31" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>676881</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6615082</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120238457</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>676849</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6615004</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120238186</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>677003</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6615007</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120236814</v>
+      </c>
+      <c r="B34" t="n">
+        <v>90075</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>676879</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6615084</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120237736</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57679</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>676936</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6615059</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120237296</v>
+      </c>
+      <c r="B36" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>677019</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6614935</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -3512,7 +3512,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120238171</v>
+        <v>120237190</v>
       </c>
       <c r="B29" t="n">
         <v>57326</v>
@@ -3548,7 +3548,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676863</v>
+        <v>677006</v>
       </c>
       <c r="R29" t="n">
-        <v>6615036</v>
+        <v>6614978</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3590,19 +3590,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3617,19 +3607,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120237190</v>
+        <v>120238171</v>
       </c>
       <c r="B30" t="n">
         <v>57326</v>
@@ -3665,7 +3655,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3674,10 +3664,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>677006</v>
+        <v>676863</v>
       </c>
       <c r="R30" t="n">
-        <v>6614978</v>
+        <v>6615036</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3707,9 +3697,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3724,12 +3724,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3838,10 +3838,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120238457</v>
+        <v>120238186</v>
       </c>
       <c r="B32" t="n">
-        <v>90527</v>
+        <v>5189</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3854,21 +3854,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676849</v>
+        <v>677003</v>
       </c>
       <c r="R32" t="n">
-        <v>6615004</v>
+        <v>6615007</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3911,19 +3911,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3938,22 +3928,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120238186</v>
+        <v>120238457</v>
       </c>
       <c r="B33" t="n">
-        <v>5189</v>
+        <v>90527</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3966,21 +3956,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3980,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>677003</v>
+        <v>676849</v>
       </c>
       <c r="R33" t="n">
-        <v>6615007</v>
+        <v>6615004</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4023,9 +4013,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4040,12 +4040,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -3512,7 +3512,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120237190</v>
+        <v>120238171</v>
       </c>
       <c r="B29" t="n">
         <v>57326</v>
@@ -3548,7 +3548,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>677006</v>
+        <v>676863</v>
       </c>
       <c r="R29" t="n">
-        <v>6614978</v>
+        <v>6615036</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3590,9 +3590,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3607,19 +3617,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120238171</v>
+        <v>120237190</v>
       </c>
       <c r="B30" t="n">
         <v>57326</v>
@@ -3655,7 +3665,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3664,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676863</v>
+        <v>677006</v>
       </c>
       <c r="R30" t="n">
-        <v>6615036</v>
+        <v>6614978</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3697,19 +3707,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3724,12 +3724,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -3512,7 +3512,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120238171</v>
+        <v>120237190</v>
       </c>
       <c r="B29" t="n">
         <v>57326</v>
@@ -3548,7 +3548,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676863</v>
+        <v>677006</v>
       </c>
       <c r="R29" t="n">
-        <v>6615036</v>
+        <v>6614978</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3590,19 +3590,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3617,19 +3607,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120237190</v>
+        <v>120238171</v>
       </c>
       <c r="B30" t="n">
         <v>57326</v>
@@ -3665,7 +3655,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3674,10 +3664,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>677006</v>
+        <v>676863</v>
       </c>
       <c r="R30" t="n">
-        <v>6614978</v>
+        <v>6615036</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3707,9 +3697,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3724,12 +3724,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3838,10 +3838,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120238186</v>
+        <v>120238457</v>
       </c>
       <c r="B32" t="n">
-        <v>5189</v>
+        <v>90527</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3854,21 +3854,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>677003</v>
+        <v>676849</v>
       </c>
       <c r="R32" t="n">
-        <v>6615007</v>
+        <v>6615004</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3911,9 +3911,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3928,22 +3938,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120238457</v>
+        <v>120238186</v>
       </c>
       <c r="B33" t="n">
-        <v>90527</v>
+        <v>5189</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3956,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3980,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676849</v>
+        <v>677003</v>
       </c>
       <c r="R33" t="n">
-        <v>6615004</v>
+        <v>6615007</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4013,19 +4023,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4040,12 +4040,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -2681,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120237239</v>
+        <v>120238186</v>
       </c>
       <c r="B21" t="n">
-        <v>57326</v>
+        <v>5189</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2693,20 +2693,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2715,21 +2715,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>677002</v>
+        <v>677003</v>
       </c>
       <c r="R21" t="n">
-        <v>6614969</v>
+        <v>6615007</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,10 +2783,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120237674</v>
+        <v>120238457</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2800,25 +2795,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2828,10 +2823,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676920</v>
+        <v>676849</v>
       </c>
       <c r="R22" t="n">
-        <v>6615057</v>
+        <v>6615004</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2861,9 +2856,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2878,22 +2883,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120237628</v>
+        <v>120237736</v>
       </c>
       <c r="B23" t="n">
-        <v>100171</v>
+        <v>57689</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2906,21 +2911,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2930,10 +2935,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676920</v>
+        <v>676936</v>
       </c>
       <c r="R23" t="n">
-        <v>6615038</v>
+        <v>6615059</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,10 +2997,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120237246</v>
+        <v>120236814</v>
       </c>
       <c r="B24" t="n">
-        <v>5189</v>
+        <v>90092</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3008,21 +3013,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>5741</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3032,10 +3037,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>677001</v>
+        <v>676879</v>
       </c>
       <c r="R24" t="n">
-        <v>6614969</v>
+        <v>6615084</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,10 +3099,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120236998</v>
+        <v>120237246</v>
       </c>
       <c r="B25" t="n">
-        <v>90527</v>
+        <v>5189</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3110,21 +3115,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3134,10 +3139,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676961</v>
+        <v>677001</v>
       </c>
       <c r="R25" t="n">
-        <v>6615062</v>
+        <v>6614969</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,10 +3201,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120237707</v>
+        <v>120236998</v>
       </c>
       <c r="B26" t="n">
-        <v>57326</v>
+        <v>90545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3208,43 +3213,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676938</v>
+        <v>676961</v>
       </c>
       <c r="R26" t="n">
-        <v>6615070</v>
+        <v>6615062</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,10 +3303,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120237606</v>
+        <v>120237628</v>
       </c>
       <c r="B27" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676929</v>
+        <v>676920</v>
       </c>
       <c r="R27" t="n">
-        <v>6614995</v>
+        <v>6615038</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3408,7 @@
         <v>120237872</v>
       </c>
       <c r="B28" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3512,10 +3512,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120238171</v>
+        <v>120237190</v>
       </c>
       <c r="B29" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676863</v>
+        <v>677006</v>
       </c>
       <c r="R29" t="n">
-        <v>6615036</v>
+        <v>6614978</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3590,19 +3590,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3617,22 +3607,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120237190</v>
+        <v>120237606</v>
       </c>
       <c r="B30" t="n">
-        <v>57326</v>
+        <v>100194</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3641,43 +3631,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>677006</v>
+        <v>676929</v>
       </c>
       <c r="R30" t="n">
-        <v>6614978</v>
+        <v>6614995</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,10 +3721,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120236816</v>
+        <v>120237674</v>
       </c>
       <c r="B31" t="n">
-        <v>100171</v>
+        <v>90598</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3748,25 +3733,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3776,10 +3761,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676881</v>
+        <v>676920</v>
       </c>
       <c r="R31" t="n">
-        <v>6615082</v>
+        <v>6615057</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,10 +3823,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120238457</v>
+        <v>120238171</v>
       </c>
       <c r="B32" t="n">
-        <v>90527</v>
+        <v>57336</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3850,38 +3835,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676849</v>
+        <v>676863</v>
       </c>
       <c r="R32" t="n">
-        <v>6615004</v>
+        <v>6615036</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3913,7 +3903,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3923,7 +3913,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3950,10 +3940,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120238186</v>
+        <v>120237707</v>
       </c>
       <c r="B33" t="n">
-        <v>5189</v>
+        <v>57336</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3962,20 +3952,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3984,16 +3974,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>677003</v>
+        <v>676938</v>
       </c>
       <c r="R33" t="n">
-        <v>6615007</v>
+        <v>6615070</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4052,10 +4047,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120236814</v>
+        <v>120237296</v>
       </c>
       <c r="B34" t="n">
-        <v>90075</v>
+        <v>100194</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4068,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5741</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4092,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676879</v>
+        <v>677019</v>
       </c>
       <c r="R34" t="n">
-        <v>6615084</v>
+        <v>6614935</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120237736</v>
+        <v>120237239</v>
       </c>
       <c r="B35" t="n">
-        <v>57679</v>
+        <v>57336</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4166,20 +4161,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4188,16 +4183,21 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676936</v>
+        <v>677002</v>
       </c>
       <c r="R35" t="n">
-        <v>6615059</v>
+        <v>6614969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120237296</v>
+        <v>120236816</v>
       </c>
       <c r="B36" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>677019</v>
+        <v>676881</v>
       </c>
       <c r="R36" t="n">
-        <v>6614935</v>
+        <v>6615082</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -2681,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120238186</v>
+        <v>120238457</v>
       </c>
       <c r="B21" t="n">
-        <v>5189</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>677003</v>
+        <v>676849</v>
       </c>
       <c r="R21" t="n">
-        <v>6615007</v>
+        <v>6615004</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,9 +2754,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2771,22 +2781,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120238457</v>
+        <v>120238186</v>
       </c>
       <c r="B22" t="n">
-        <v>90545</v>
+        <v>5189</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,21 +2809,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2823,10 +2833,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676849</v>
+        <v>677003</v>
       </c>
       <c r="R22" t="n">
-        <v>6615004</v>
+        <v>6615007</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,19 +2866,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2883,12 +2883,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2681,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120238457</v>
+        <v>120237872</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2693,38 +2693,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676849</v>
+        <v>677009</v>
       </c>
       <c r="R21" t="n">
-        <v>6615004</v>
+        <v>6615043</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,19 +2759,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2781,12 +2776,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2895,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120237736</v>
+        <v>120237674</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>90598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2907,25 +2902,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2935,10 +2930,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676936</v>
+        <v>676920</v>
       </c>
       <c r="R23" t="n">
-        <v>6615059</v>
+        <v>6615057</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,10 +2992,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120236814</v>
+        <v>120237707</v>
       </c>
       <c r="B24" t="n">
-        <v>90092</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3009,38 +3004,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5741</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676879</v>
+        <v>676938</v>
       </c>
       <c r="R24" t="n">
-        <v>6615084</v>
+        <v>6615070</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,10 +3099,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120237246</v>
+        <v>120236816</v>
       </c>
       <c r="B25" t="n">
-        <v>5189</v>
+        <v>100194</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3115,21 +3115,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>677001</v>
+        <v>676881</v>
       </c>
       <c r="R25" t="n">
-        <v>6614969</v>
+        <v>6615082</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120237628</v>
+        <v>120237296</v>
       </c>
       <c r="B27" t="n">
         <v>100194</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676920</v>
+        <v>677019</v>
       </c>
       <c r="R27" t="n">
-        <v>6615038</v>
+        <v>6614935</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120237872</v>
+        <v>120238457</v>
       </c>
       <c r="B28" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3417,43 +3417,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>677009</v>
+        <v>676849</v>
       </c>
       <c r="R28" t="n">
-        <v>6615043</v>
+        <v>6615004</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3483,9 +3478,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3500,19 +3505,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120237190</v>
+        <v>120237239</v>
       </c>
       <c r="B29" t="n">
         <v>57336</v>
@@ -3548,7 +3553,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3557,10 +3562,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>677006</v>
+        <v>677002</v>
       </c>
       <c r="R29" t="n">
-        <v>6614978</v>
+        <v>6614969</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,10 +3624,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120237606</v>
+        <v>120237190</v>
       </c>
       <c r="B30" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3631,38 +3636,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676929</v>
+        <v>677006</v>
       </c>
       <c r="R30" t="n">
-        <v>6614995</v>
+        <v>6614978</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,10 +3731,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120237674</v>
+        <v>120237628</v>
       </c>
       <c r="B31" t="n">
-        <v>90598</v>
+        <v>100194</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3733,25 +3743,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3764,7 +3774,7 @@
         <v>676920</v>
       </c>
       <c r="R31" t="n">
-        <v>6615057</v>
+        <v>6615038</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,10 +3833,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120238171</v>
+        <v>120236814</v>
       </c>
       <c r="B32" t="n">
-        <v>57336</v>
+        <v>90092</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3835,43 +3845,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>5741</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676863</v>
+        <v>676879</v>
       </c>
       <c r="R32" t="n">
-        <v>6615036</v>
+        <v>6615084</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3901,19 +3906,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3928,19 +3923,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120237707</v>
+        <v>120238171</v>
       </c>
       <c r="B33" t="n">
         <v>57336</v>
@@ -3985,10 +3980,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676938</v>
+        <v>676863</v>
       </c>
       <c r="R33" t="n">
-        <v>6615070</v>
+        <v>6615036</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4018,9 +4013,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4035,22 +4040,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120237296</v>
+        <v>120237246</v>
       </c>
       <c r="B34" t="n">
-        <v>100194</v>
+        <v>5189</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4063,21 +4068,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>677019</v>
+        <v>677001</v>
       </c>
       <c r="R34" t="n">
-        <v>6614935</v>
+        <v>6614969</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4149,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120237239</v>
+        <v>120237736</v>
       </c>
       <c r="B35" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4161,20 +4166,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4183,21 +4188,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>677002</v>
+        <v>676936</v>
       </c>
       <c r="R35" t="n">
-        <v>6614969</v>
+        <v>6615059</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,7 +4256,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120236816</v>
+        <v>120237606</v>
       </c>
       <c r="B36" t="n">
         <v>100194</v>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676881</v>
+        <v>676929</v>
       </c>
       <c r="R36" t="n">
-        <v>6615082</v>
+        <v>6614995</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4355,6 +4355,1100 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120399210</v>
+      </c>
+      <c r="B37" t="n">
+        <v>8432</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>677015</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6615092</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120398695</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90545</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>676856</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6614998</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120399258</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8432</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>677042</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6614994</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120399055</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90545</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>676930</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6615106</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120399238</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8421</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>677043</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6615044</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120398837</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>676918</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6615032</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120399303</v>
+      </c>
+      <c r="B43" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>677012</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6614962</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120399252</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>677049</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6615010</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120398811</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>676903</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6615027</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120398946</v>
+      </c>
+      <c r="B46" t="n">
+        <v>90934</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>676919</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6615041</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -2681,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120237872</v>
+        <v>120237674</v>
       </c>
       <c r="B21" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2697,39 +2697,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>677009</v>
+        <v>676920</v>
       </c>
       <c r="R21" t="n">
-        <v>6615043</v>
+        <v>6615057</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,10 +2783,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120238186</v>
+        <v>120237872</v>
       </c>
       <c r="B22" t="n">
-        <v>5189</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2800,20 +2795,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2822,16 +2817,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>677003</v>
+        <v>677009</v>
       </c>
       <c r="R22" t="n">
-        <v>6615007</v>
+        <v>6615043</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120237674</v>
+        <v>120238186</v>
       </c>
       <c r="B23" t="n">
-        <v>90598</v>
+        <v>5189</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2902,25 +2902,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676920</v>
+        <v>677003</v>
       </c>
       <c r="R23" t="n">
-        <v>6615057</v>
+        <v>6615007</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,10 +2992,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120237707</v>
+        <v>120236816</v>
       </c>
       <c r="B24" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3004,43 +3004,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676938</v>
+        <v>676881</v>
       </c>
       <c r="R24" t="n">
-        <v>6615070</v>
+        <v>6615082</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120236816</v>
+        <v>120237707</v>
       </c>
       <c r="B25" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3111,38 +3106,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676881</v>
+        <v>676938</v>
       </c>
       <c r="R25" t="n">
-        <v>6615082</v>
+        <v>6615070</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120237246</v>
+        <v>120237736</v>
       </c>
       <c r="B34" t="n">
-        <v>5189</v>
+        <v>57689</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4068,16 +4068,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>677001</v>
+        <v>676936</v>
       </c>
       <c r="R34" t="n">
-        <v>6614969</v>
+        <v>6615059</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120237736</v>
+        <v>120237246</v>
       </c>
       <c r="B35" t="n">
-        <v>57689</v>
+        <v>5189</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4170,16 +4170,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676936</v>
+        <v>677001</v>
       </c>
       <c r="R35" t="n">
-        <v>6615059</v>
+        <v>6614969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -2681,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120237674</v>
+        <v>120237736</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>57689</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2693,25 +2693,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676920</v>
+        <v>676936</v>
       </c>
       <c r="R21" t="n">
-        <v>6615057</v>
+        <v>6615059</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,10 +2783,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120237872</v>
+        <v>120236998</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2795,43 +2795,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>677009</v>
+        <v>676961</v>
       </c>
       <c r="R22" t="n">
-        <v>6615043</v>
+        <v>6615062</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,10 +2885,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120238186</v>
+        <v>120237872</v>
       </c>
       <c r="B23" t="n">
-        <v>5189</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2902,20 +2897,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2924,16 +2919,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>677003</v>
+        <v>677009</v>
       </c>
       <c r="R23" t="n">
-        <v>6615007</v>
+        <v>6615043</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,10 +2992,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120236816</v>
+        <v>120236814</v>
       </c>
       <c r="B24" t="n">
-        <v>100194</v>
+        <v>90092</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3008,21 +3008,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5741</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676881</v>
+        <v>676879</v>
       </c>
       <c r="R24" t="n">
-        <v>6615082</v>
+        <v>6615084</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120237707</v>
+        <v>120238186</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>5189</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3106,20 +3106,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3128,21 +3128,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676938</v>
+        <v>677003</v>
       </c>
       <c r="R25" t="n">
-        <v>6615070</v>
+        <v>6615007</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,10 +3196,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120236998</v>
+        <v>120237190</v>
       </c>
       <c r="B26" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3213,38 +3208,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676961</v>
+        <v>677006</v>
       </c>
       <c r="R26" t="n">
-        <v>6615062</v>
+        <v>6614978</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,10 +3303,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120237296</v>
+        <v>120238171</v>
       </c>
       <c r="B27" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3315,38 +3315,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>677019</v>
+        <v>676863</v>
       </c>
       <c r="R27" t="n">
-        <v>6614935</v>
+        <v>6615036</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3376,9 +3381,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3393,12 +3408,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3517,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120237239</v>
+        <v>120237246</v>
       </c>
       <c r="B29" t="n">
-        <v>57336</v>
+        <v>5189</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3529,20 +3544,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3551,18 +3566,13 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>677002</v>
+        <v>677001</v>
       </c>
       <c r="R29" t="n">
         <v>6614969</v>
@@ -3624,7 +3634,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120237190</v>
+        <v>120237239</v>
       </c>
       <c r="B30" t="n">
         <v>57336</v>
@@ -3660,7 +3670,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3669,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>677006</v>
+        <v>677002</v>
       </c>
       <c r="R30" t="n">
-        <v>6614978</v>
+        <v>6614969</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,10 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120237628</v>
+        <v>120237707</v>
       </c>
       <c r="B31" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3743,38 +3753,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676920</v>
+        <v>676938</v>
       </c>
       <c r="R31" t="n">
-        <v>6615038</v>
+        <v>6615070</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3833,10 +3848,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120236814</v>
+        <v>120237296</v>
       </c>
       <c r="B32" t="n">
-        <v>90092</v>
+        <v>100194</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3849,21 +3864,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5741</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3873,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676879</v>
+        <v>677019</v>
       </c>
       <c r="R32" t="n">
-        <v>6615084</v>
+        <v>6614935</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120238171</v>
+        <v>120237674</v>
       </c>
       <c r="B33" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3951,39 +3966,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676863</v>
+        <v>676920</v>
       </c>
       <c r="R33" t="n">
-        <v>6615036</v>
+        <v>6615057</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4013,19 +4023,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4040,22 +4040,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120237736</v>
+        <v>120237606</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>100194</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4068,21 +4068,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676936</v>
+        <v>676929</v>
       </c>
       <c r="R34" t="n">
-        <v>6615059</v>
+        <v>6614995</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120237246</v>
+        <v>120237628</v>
       </c>
       <c r="B35" t="n">
-        <v>5189</v>
+        <v>100194</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4170,21 +4170,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>677001</v>
+        <v>676920</v>
       </c>
       <c r="R35" t="n">
-        <v>6614969</v>
+        <v>6615038</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,7 +4256,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120237606</v>
+        <v>120236816</v>
       </c>
       <c r="B36" t="n">
         <v>100194</v>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676929</v>
+        <v>676881</v>
       </c>
       <c r="R36" t="n">
-        <v>6614995</v>
+        <v>6615082</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120399258</v>
+        <v>120399238</v>
       </c>
       <c r="B39" t="n">
-        <v>8432</v>
+        <v>8421</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>677042</v>
+        <v>677043</v>
       </c>
       <c r="R39" t="n">
-        <v>6614994</v>
+        <v>6615044</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4692,10 +4692,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120399055</v>
+        <v>120399252</v>
       </c>
       <c r="B40" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4704,38 +4704,46 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676930</v>
+        <v>677049</v>
       </c>
       <c r="R40" t="n">
-        <v>6615106</v>
+        <v>6615010</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4798,10 +4806,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120399238</v>
+        <v>120399258</v>
       </c>
       <c r="B41" t="n">
-        <v>8421</v>
+        <v>8432</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4814,21 +4822,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4847,10 +4855,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>677043</v>
+        <v>677042</v>
       </c>
       <c r="R41" t="n">
-        <v>6615044</v>
+        <v>6614994</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4914,10 +4922,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120398837</v>
+        <v>120398946</v>
       </c>
       <c r="B42" t="n">
-        <v>91881</v>
+        <v>90934</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4926,25 +4934,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>1506</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4954,10 +4962,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676918</v>
+        <v>676919</v>
       </c>
       <c r="R42" t="n">
-        <v>6615032</v>
+        <v>6615041</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5020,10 +5028,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120399303</v>
+        <v>120398811</v>
       </c>
       <c r="B43" t="n">
-        <v>100194</v>
+        <v>91881</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5032,25 +5040,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5060,10 +5068,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>677012</v>
+        <v>676903</v>
       </c>
       <c r="R43" t="n">
-        <v>6614962</v>
+        <v>6615027</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5126,10 +5134,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120399252</v>
+        <v>120399055</v>
       </c>
       <c r="B44" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5138,46 +5146,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>677049</v>
+        <v>676930</v>
       </c>
       <c r="R44" t="n">
-        <v>6615010</v>
+        <v>6615106</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5240,10 +5240,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120398811</v>
+        <v>120399303</v>
       </c>
       <c r="B45" t="n">
-        <v>91881</v>
+        <v>100194</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5252,25 +5252,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676903</v>
+        <v>677012</v>
       </c>
       <c r="R45" t="n">
-        <v>6615027</v>
+        <v>6614962</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120398946</v>
+        <v>120398837</v>
       </c>
       <c r="B46" t="n">
-        <v>90934</v>
+        <v>91881</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5358,25 +5358,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1506</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>676919</v>
+        <v>676918</v>
       </c>
       <c r="R46" t="n">
-        <v>6615041</v>
+        <v>6615032</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -3950,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120237674</v>
+        <v>120237606</v>
       </c>
       <c r="B33" t="n">
-        <v>90598</v>
+        <v>100194</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3962,25 +3962,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676920</v>
+        <v>676929</v>
       </c>
       <c r="R33" t="n">
-        <v>6615057</v>
+        <v>6614995</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120237606</v>
+        <v>120237674</v>
       </c>
       <c r="B34" t="n">
-        <v>100194</v>
+        <v>90598</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4064,25 +4064,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676929</v>
+        <v>676920</v>
       </c>
       <c r="R34" t="n">
-        <v>6614995</v>
+        <v>6615057</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -2681,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120237736</v>
+        <v>120237246</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>5189</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676936</v>
+        <v>677001</v>
       </c>
       <c r="R21" t="n">
-        <v>6615059</v>
+        <v>6614969</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120237872</v>
+        <v>120238171</v>
       </c>
       <c r="B23" t="n">
         <v>57336</v>
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>677009</v>
+        <v>676863</v>
       </c>
       <c r="R23" t="n">
-        <v>6615043</v>
+        <v>6615036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,9 +2963,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2980,22 +2990,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120236814</v>
+        <v>120237872</v>
       </c>
       <c r="B24" t="n">
-        <v>90092</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3004,38 +3014,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5741</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676879</v>
+        <v>677009</v>
       </c>
       <c r="R24" t="n">
-        <v>6615084</v>
+        <v>6615043</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,10 +3109,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120238186</v>
+        <v>120237296</v>
       </c>
       <c r="B25" t="n">
-        <v>5189</v>
+        <v>100194</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3110,21 +3125,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3134,10 +3149,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>677003</v>
+        <v>677019</v>
       </c>
       <c r="R25" t="n">
-        <v>6615007</v>
+        <v>6614935</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,10 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120237190</v>
+        <v>120236814</v>
       </c>
       <c r="B26" t="n">
-        <v>57336</v>
+        <v>90092</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3208,43 +3223,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5741</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>677006</v>
+        <v>676879</v>
       </c>
       <c r="R26" t="n">
-        <v>6614978</v>
+        <v>6615084</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,10 +3313,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120238171</v>
+        <v>120238186</v>
       </c>
       <c r="B27" t="n">
-        <v>57336</v>
+        <v>5189</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3315,20 +3325,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3337,21 +3347,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676863</v>
+        <v>677003</v>
       </c>
       <c r="R27" t="n">
-        <v>6615036</v>
+        <v>6615007</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3381,19 +3386,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3408,12 +3403,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3532,10 +3527,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120237246</v>
+        <v>120237239</v>
       </c>
       <c r="B29" t="n">
-        <v>5189</v>
+        <v>57336</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3544,20 +3539,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3566,13 +3561,18 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>677001</v>
+        <v>677002</v>
       </c>
       <c r="R29" t="n">
         <v>6614969</v>
@@ -3634,10 +3634,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120237239</v>
+        <v>120237674</v>
       </c>
       <c r="B30" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3650,39 +3650,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>677002</v>
+        <v>676920</v>
       </c>
       <c r="R30" t="n">
-        <v>6614969</v>
+        <v>6615057</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,10 +3736,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120237707</v>
+        <v>120237606</v>
       </c>
       <c r="B31" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3753,43 +3748,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676938</v>
+        <v>676929</v>
       </c>
       <c r="R31" t="n">
-        <v>6615070</v>
+        <v>6614995</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3838,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120237296</v>
+        <v>120236816</v>
       </c>
       <c r="B32" t="n">
         <v>100194</v>
@@ -3888,10 +3878,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>677019</v>
+        <v>676881</v>
       </c>
       <c r="R32" t="n">
-        <v>6614935</v>
+        <v>6615082</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,10 +3940,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120237606</v>
+        <v>120237190</v>
       </c>
       <c r="B33" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3962,38 +3952,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676929</v>
+        <v>677006</v>
       </c>
       <c r="R33" t="n">
-        <v>6614995</v>
+        <v>6614978</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4052,10 +4047,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120237674</v>
+        <v>120237707</v>
       </c>
       <c r="B34" t="n">
-        <v>90598</v>
+        <v>57336</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4068,34 +4063,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676920</v>
+        <v>676938</v>
       </c>
       <c r="R34" t="n">
-        <v>6615057</v>
+        <v>6615070</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120237628</v>
+        <v>120237736</v>
       </c>
       <c r="B35" t="n">
-        <v>100194</v>
+        <v>57689</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4170,21 +4170,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676920</v>
+        <v>676936</v>
       </c>
       <c r="R35" t="n">
-        <v>6615038</v>
+        <v>6615059</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,7 +4256,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120236816</v>
+        <v>120237628</v>
       </c>
       <c r="B36" t="n">
         <v>100194</v>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676881</v>
+        <v>676920</v>
       </c>
       <c r="R36" t="n">
-        <v>6615082</v>
+        <v>6615038</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120399238</v>
+        <v>120399303</v>
       </c>
       <c r="B39" t="n">
-        <v>8421</v>
+        <v>100194</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4592,43 +4592,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>677043</v>
+        <v>677012</v>
       </c>
       <c r="R39" t="n">
-        <v>6615044</v>
+        <v>6614962</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4669,7 +4660,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4806,10 +4796,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120399258</v>
+        <v>120398811</v>
       </c>
       <c r="B41" t="n">
-        <v>8432</v>
+        <v>91881</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4818,47 +4808,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>677042</v>
+        <v>676903</v>
       </c>
       <c r="R41" t="n">
-        <v>6614994</v>
+        <v>6615027</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4899,7 +4880,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5028,10 +5008,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120398811</v>
+        <v>120399055</v>
       </c>
       <c r="B43" t="n">
-        <v>91881</v>
+        <v>90545</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5040,25 +5020,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5068,10 +5048,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676903</v>
+        <v>676930</v>
       </c>
       <c r="R43" t="n">
-        <v>6615027</v>
+        <v>6615106</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5134,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120399055</v>
+        <v>120399238</v>
       </c>
       <c r="B44" t="n">
-        <v>90545</v>
+        <v>8421</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5150,34 +5130,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>676930</v>
+        <v>677043</v>
       </c>
       <c r="R44" t="n">
-        <v>6615106</v>
+        <v>6615044</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5218,6 +5207,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5240,10 +5230,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120399303</v>
+        <v>120399258</v>
       </c>
       <c r="B45" t="n">
-        <v>100194</v>
+        <v>8432</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5256,34 +5246,43 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>677012</v>
+        <v>677042</v>
       </c>
       <c r="R45" t="n">
-        <v>6614962</v>
+        <v>6614994</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5324,6 +5323,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -2681,7 +2681,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120237246</v>
+        <v>120238186</v>
       </c>
       <c r="B21" t="n">
         <v>5189</v>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>677001</v>
+        <v>677003</v>
       </c>
       <c r="R21" t="n">
-        <v>6614969</v>
+        <v>6615007</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,10 +2783,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120236998</v>
+        <v>120236816</v>
       </c>
       <c r="B22" t="n">
-        <v>90545</v>
+        <v>100194</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,21 +2799,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676961</v>
+        <v>676881</v>
       </c>
       <c r="R22" t="n">
-        <v>6615062</v>
+        <v>6615082</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120238171</v>
+        <v>120236814</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>90092</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2897,43 +2897,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5741</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676863</v>
+        <v>676879</v>
       </c>
       <c r="R23" t="n">
-        <v>6615036</v>
+        <v>6615084</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,19 +2958,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2990,22 +2975,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120237872</v>
+        <v>120237736</v>
       </c>
       <c r="B24" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3014,20 +2999,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3036,21 +3021,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>677009</v>
+        <v>676936</v>
       </c>
       <c r="R24" t="n">
-        <v>6615043</v>
+        <v>6615059</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3211,10 +3191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120236814</v>
+        <v>120237239</v>
       </c>
       <c r="B26" t="n">
-        <v>90092</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3223,38 +3203,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5741</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676879</v>
+        <v>677002</v>
       </c>
       <c r="R26" t="n">
-        <v>6615084</v>
+        <v>6614969</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,10 +3298,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120238186</v>
+        <v>120237190</v>
       </c>
       <c r="B27" t="n">
-        <v>5189</v>
+        <v>57336</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3325,20 +3310,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3347,16 +3332,21 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>677003</v>
+        <v>677006</v>
       </c>
       <c r="R27" t="n">
-        <v>6615007</v>
+        <v>6614978</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,10 +3405,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120238457</v>
+        <v>120237628</v>
       </c>
       <c r="B28" t="n">
-        <v>90545</v>
+        <v>100194</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3431,21 +3421,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3455,10 +3445,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676849</v>
+        <v>676920</v>
       </c>
       <c r="R28" t="n">
-        <v>6615004</v>
+        <v>6615038</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3488,19 +3478,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3515,22 +3495,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120237239</v>
+        <v>120237246</v>
       </c>
       <c r="B29" t="n">
-        <v>57336</v>
+        <v>5189</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3539,20 +3519,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3561,18 +3541,13 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>677002</v>
+        <v>677001</v>
       </c>
       <c r="R29" t="n">
         <v>6614969</v>
@@ -3634,10 +3609,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120237674</v>
+        <v>120236998</v>
       </c>
       <c r="B30" t="n">
-        <v>90598</v>
+        <v>90545</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3646,25 +3621,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3674,10 +3649,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676920</v>
+        <v>676961</v>
       </c>
       <c r="R30" t="n">
-        <v>6615057</v>
+        <v>6615062</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,10 +3711,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120237606</v>
+        <v>120238457</v>
       </c>
       <c r="B31" t="n">
-        <v>100194</v>
+        <v>90545</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3752,21 +3727,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3776,10 +3751,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676929</v>
+        <v>676849</v>
       </c>
       <c r="R31" t="n">
-        <v>6614995</v>
+        <v>6615004</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3809,9 +3784,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3826,22 +3811,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120236816</v>
+        <v>120237674</v>
       </c>
       <c r="B32" t="n">
-        <v>100194</v>
+        <v>90598</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3850,25 +3835,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3878,10 +3863,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676881</v>
+        <v>676920</v>
       </c>
       <c r="R32" t="n">
-        <v>6615082</v>
+        <v>6615057</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,7 +3925,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120237190</v>
+        <v>120238171</v>
       </c>
       <c r="B33" t="n">
         <v>57336</v>
@@ -3976,7 +3961,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3985,10 +3970,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>677006</v>
+        <v>676863</v>
       </c>
       <c r="R33" t="n">
-        <v>6614978</v>
+        <v>6615036</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4018,9 +4003,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4035,12 +4030,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4154,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120237736</v>
+        <v>120237606</v>
       </c>
       <c r="B35" t="n">
-        <v>57689</v>
+        <v>100194</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4170,21 +4165,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4194,10 +4189,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676936</v>
+        <v>676929</v>
       </c>
       <c r="R35" t="n">
-        <v>6615059</v>
+        <v>6614995</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,10 +4251,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120237628</v>
+        <v>120237872</v>
       </c>
       <c r="B36" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4268,38 +4263,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>676920</v>
+        <v>677009</v>
       </c>
       <c r="R36" t="n">
-        <v>6615038</v>
+        <v>6615043</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120399210</v>
+        <v>120399238</v>
       </c>
       <c r="B37" t="n">
-        <v>8432</v>
+        <v>8421</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>677015</v>
+        <v>677043</v>
       </c>
       <c r="R37" t="n">
-        <v>6615092</v>
+        <v>6615044</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120398695</v>
+        <v>120398811</v>
       </c>
       <c r="B38" t="n">
-        <v>90545</v>
+        <v>91881</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4486,25 +4486,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676856</v>
+        <v>676903</v>
       </c>
       <c r="R38" t="n">
-        <v>6614998</v>
+        <v>6615027</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4564,22 +4564,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120399303</v>
+        <v>120398695</v>
       </c>
       <c r="B39" t="n">
-        <v>100194</v>
+        <v>90545</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4592,21 +4596,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4616,10 +4620,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>677012</v>
+        <v>676856</v>
       </c>
       <c r="R39" t="n">
-        <v>6614962</v>
+        <v>6614998</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,26 +4670,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120399252</v>
+        <v>120399303</v>
       </c>
       <c r="B40" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4694,46 +4694,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>677049</v>
+        <v>677012</v>
       </c>
       <c r="R40" t="n">
-        <v>6615010</v>
+        <v>6614962</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4796,10 +4788,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120398811</v>
+        <v>120399055</v>
       </c>
       <c r="B41" t="n">
-        <v>91881</v>
+        <v>90545</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4808,25 +4800,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4836,10 +4828,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>676903</v>
+        <v>676930</v>
       </c>
       <c r="R41" t="n">
-        <v>6615027</v>
+        <v>6615106</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4902,10 +4894,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120398946</v>
+        <v>120399258</v>
       </c>
       <c r="B42" t="n">
-        <v>90934</v>
+        <v>8432</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4914,38 +4906,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1506</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676919</v>
+        <v>677042</v>
       </c>
       <c r="R42" t="n">
-        <v>6615041</v>
+        <v>6614994</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4986,6 +4987,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5008,10 +5010,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120399055</v>
+        <v>120399252</v>
       </c>
       <c r="B43" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5020,38 +5022,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676930</v>
+        <v>677049</v>
       </c>
       <c r="R43" t="n">
-        <v>6615106</v>
+        <v>6615010</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5114,10 +5124,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120399238</v>
+        <v>120398946</v>
       </c>
       <c r="B44" t="n">
-        <v>8421</v>
+        <v>90934</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5126,47 +5136,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106554</v>
+        <v>1506</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>677043</v>
+        <v>676919</v>
       </c>
       <c r="R44" t="n">
-        <v>6615044</v>
+        <v>6615041</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5208,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5230,7 +5230,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120399258</v>
+        <v>120399210</v>
       </c>
       <c r="B45" t="n">
         <v>8432</v>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>677042</v>
+        <v>677015</v>
       </c>
       <c r="R45" t="n">
-        <v>6614994</v>
+        <v>6615092</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -2783,10 +2783,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120236816</v>
+        <v>120236814</v>
       </c>
       <c r="B22" t="n">
-        <v>100194</v>
+        <v>90092</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,21 +2799,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>5741</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676881</v>
+        <v>676879</v>
       </c>
       <c r="R22" t="n">
-        <v>6615082</v>
+        <v>6615084</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120236814</v>
+        <v>120236816</v>
       </c>
       <c r="B23" t="n">
-        <v>90092</v>
+        <v>100194</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2901,21 +2901,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5741</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676879</v>
+        <v>676881</v>
       </c>
       <c r="R23" t="n">
-        <v>6615084</v>
+        <v>6615082</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -2681,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120238186</v>
+        <v>120237736</v>
       </c>
       <c r="B21" t="n">
-        <v>5189</v>
+        <v>57689</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>677003</v>
+        <v>676936</v>
       </c>
       <c r="R21" t="n">
-        <v>6615007</v>
+        <v>6615059</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,10 +2783,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120236814</v>
+        <v>120237606</v>
       </c>
       <c r="B22" t="n">
-        <v>90092</v>
+        <v>100194</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,21 +2799,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5741</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676879</v>
+        <v>676929</v>
       </c>
       <c r="R22" t="n">
-        <v>6615084</v>
+        <v>6614995</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120236816</v>
+        <v>120237628</v>
       </c>
       <c r="B23" t="n">
         <v>100194</v>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676881</v>
+        <v>676920</v>
       </c>
       <c r="R23" t="n">
-        <v>6615082</v>
+        <v>6615038</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,10 +2987,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120237736</v>
+        <v>120237246</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>5189</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3003,16 +3003,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676936</v>
+        <v>677001</v>
       </c>
       <c r="R24" t="n">
-        <v>6615059</v>
+        <v>6614969</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,10 +3089,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120237296</v>
+        <v>120237239</v>
       </c>
       <c r="B25" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3101,38 +3101,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>677019</v>
+        <v>677002</v>
       </c>
       <c r="R25" t="n">
-        <v>6614935</v>
+        <v>6614969</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,10 +3196,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120237239</v>
+        <v>120237674</v>
       </c>
       <c r="B26" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3207,39 +3212,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>677002</v>
+        <v>676920</v>
       </c>
       <c r="R26" t="n">
-        <v>6614969</v>
+        <v>6615057</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,10 +3298,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120237190</v>
+        <v>120238186</v>
       </c>
       <c r="B27" t="n">
-        <v>57336</v>
+        <v>5189</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3310,20 +3310,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3332,21 +3332,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>677006</v>
+        <v>677003</v>
       </c>
       <c r="R27" t="n">
-        <v>6614978</v>
+        <v>6615007</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,10 +3400,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120237628</v>
+        <v>120237707</v>
       </c>
       <c r="B28" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3417,38 +3412,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676920</v>
+        <v>676938</v>
       </c>
       <c r="R28" t="n">
-        <v>6615038</v>
+        <v>6615070</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3507,10 +3507,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120237246</v>
+        <v>120237296</v>
       </c>
       <c r="B29" t="n">
-        <v>5189</v>
+        <v>100194</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3523,21 +3523,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>677001</v>
+        <v>677019</v>
       </c>
       <c r="R29" t="n">
-        <v>6614969</v>
+        <v>6614935</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3823,10 +3823,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120237674</v>
+        <v>120236816</v>
       </c>
       <c r="B32" t="n">
-        <v>90598</v>
+        <v>100194</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3835,25 +3835,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676920</v>
+        <v>676881</v>
       </c>
       <c r="R32" t="n">
-        <v>6615057</v>
+        <v>6615082</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,10 +3925,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120238171</v>
+        <v>120236814</v>
       </c>
       <c r="B33" t="n">
-        <v>57336</v>
+        <v>90092</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3937,43 +3937,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>5741</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676863</v>
+        <v>676879</v>
       </c>
       <c r="R33" t="n">
-        <v>6615036</v>
+        <v>6615084</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4003,19 +3998,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4030,19 +4015,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120237707</v>
+        <v>120238171</v>
       </c>
       <c r="B34" t="n">
         <v>57336</v>
@@ -4087,10 +4072,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676938</v>
+        <v>676863</v>
       </c>
       <c r="R34" t="n">
-        <v>6615070</v>
+        <v>6615036</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4120,9 +4105,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4137,22 +4132,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120237606</v>
+        <v>120237872</v>
       </c>
       <c r="B35" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4161,38 +4156,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676929</v>
+        <v>677009</v>
       </c>
       <c r="R35" t="n">
-        <v>6614995</v>
+        <v>6615043</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4251,7 +4251,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120237872</v>
+        <v>120237190</v>
       </c>
       <c r="B36" t="n">
         <v>57336</v>
@@ -4287,7 +4287,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>677009</v>
+        <v>677006</v>
       </c>
       <c r="R36" t="n">
-        <v>6615043</v>
+        <v>6614978</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120399238</v>
+        <v>120398837</v>
       </c>
       <c r="B37" t="n">
-        <v>8421</v>
+        <v>91881</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4370,47 +4370,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>677043</v>
+        <v>676918</v>
       </c>
       <c r="R37" t="n">
-        <v>6615044</v>
+        <v>6615032</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4451,7 +4442,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4474,10 +4464,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120398811</v>
+        <v>120399252</v>
       </c>
       <c r="B38" t="n">
-        <v>91881</v>
+        <v>57336</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4490,34 +4480,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676903</v>
+        <v>677049</v>
       </c>
       <c r="R38" t="n">
-        <v>6615027</v>
+        <v>6615010</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4580,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120398695</v>
+        <v>120399210</v>
       </c>
       <c r="B39" t="n">
-        <v>90545</v>
+        <v>8432</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4596,34 +4594,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>676856</v>
+        <v>677015</v>
       </c>
       <c r="R39" t="n">
-        <v>6614998</v>
+        <v>6615092</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4664,21 +4671,26 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4894,10 +4906,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120399258</v>
+        <v>120398811</v>
       </c>
       <c r="B42" t="n">
-        <v>8432</v>
+        <v>91881</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4906,47 +4918,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>677042</v>
+        <v>676903</v>
       </c>
       <c r="R42" t="n">
-        <v>6614994</v>
+        <v>6615027</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4987,7 +4990,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5010,10 +5012,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120399252</v>
+        <v>120399258</v>
       </c>
       <c r="B43" t="n">
-        <v>57336</v>
+        <v>8432</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5022,33 +5024,34 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5058,10 +5061,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>677049</v>
+        <v>677042</v>
       </c>
       <c r="R43" t="n">
-        <v>6615010</v>
+        <v>6614994</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5102,6 +5105,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5124,10 +5128,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120398946</v>
+        <v>120398695</v>
       </c>
       <c r="B44" t="n">
-        <v>90934</v>
+        <v>90545</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5136,25 +5140,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1506</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5164,10 +5168,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>676919</v>
+        <v>676856</v>
       </c>
       <c r="R44" t="n">
-        <v>6615041</v>
+        <v>6614998</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5214,26 +5218,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120399210</v>
+        <v>120399238</v>
       </c>
       <c r="B45" t="n">
-        <v>8432</v>
+        <v>8421</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5246,21 +5246,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>677015</v>
+        <v>677043</v>
       </c>
       <c r="R45" t="n">
-        <v>6615092</v>
+        <v>6615044</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120398837</v>
+        <v>120398946</v>
       </c>
       <c r="B46" t="n">
-        <v>91881</v>
+        <v>90934</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5358,25 +5358,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>1506</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>676918</v>
+        <v>676919</v>
       </c>
       <c r="R46" t="n">
-        <v>6615032</v>
+        <v>6615041</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -2681,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120237736</v>
+        <v>120237872</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2693,20 +2693,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2715,16 +2715,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676936</v>
+        <v>677009</v>
       </c>
       <c r="R21" t="n">
-        <v>6615059</v>
+        <v>6615043</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2788,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120237606</v>
+        <v>120237628</v>
       </c>
       <c r="B22" t="n">
         <v>100194</v>
@@ -2823,10 +2828,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676929</v>
+        <v>676920</v>
       </c>
       <c r="R22" t="n">
-        <v>6614995</v>
+        <v>6615038</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120237628</v>
+        <v>120237707</v>
       </c>
       <c r="B23" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2897,38 +2902,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676920</v>
+        <v>676938</v>
       </c>
       <c r="R23" t="n">
-        <v>6615038</v>
+        <v>6615070</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,10 +3099,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120237239</v>
+        <v>120236814</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>90092</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3101,43 +3111,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5741</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>677002</v>
+        <v>676879</v>
       </c>
       <c r="R25" t="n">
-        <v>6614969</v>
+        <v>6615084</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,10 +3201,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120237674</v>
+        <v>120237296</v>
       </c>
       <c r="B26" t="n">
-        <v>90598</v>
+        <v>100194</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3208,25 +3213,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3236,10 +3241,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676920</v>
+        <v>677019</v>
       </c>
       <c r="R26" t="n">
-        <v>6615057</v>
+        <v>6614935</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,10 +3303,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120238186</v>
+        <v>120236816</v>
       </c>
       <c r="B27" t="n">
-        <v>5189</v>
+        <v>100194</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3314,21 +3319,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3338,10 +3343,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>677003</v>
+        <v>676881</v>
       </c>
       <c r="R27" t="n">
-        <v>6615007</v>
+        <v>6615082</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,7 +3405,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120237707</v>
+        <v>120237239</v>
       </c>
       <c r="B28" t="n">
         <v>57336</v>
@@ -3445,10 +3450,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676938</v>
+        <v>677002</v>
       </c>
       <c r="R28" t="n">
-        <v>6615070</v>
+        <v>6614969</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3507,10 +3512,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120237296</v>
+        <v>120238457</v>
       </c>
       <c r="B29" t="n">
-        <v>100194</v>
+        <v>90545</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3523,21 +3528,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3547,10 +3552,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>677019</v>
+        <v>676849</v>
       </c>
       <c r="R29" t="n">
-        <v>6614935</v>
+        <v>6615004</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3580,9 +3585,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3597,12 +3612,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3711,10 +3726,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120238457</v>
+        <v>120237674</v>
       </c>
       <c r="B31" t="n">
-        <v>90545</v>
+        <v>90598</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3723,25 +3738,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3751,10 +3766,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676849</v>
+        <v>676920</v>
       </c>
       <c r="R31" t="n">
-        <v>6615004</v>
+        <v>6615057</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3784,19 +3799,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3811,19 +3816,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120236816</v>
+        <v>120237606</v>
       </c>
       <c r="B32" t="n">
         <v>100194</v>
@@ -3863,10 +3868,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676881</v>
+        <v>676929</v>
       </c>
       <c r="R32" t="n">
-        <v>6615082</v>
+        <v>6614995</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,10 +3930,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120236814</v>
+        <v>120238171</v>
       </c>
       <c r="B33" t="n">
-        <v>90092</v>
+        <v>57336</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3937,38 +3942,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5741</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676879</v>
+        <v>676863</v>
       </c>
       <c r="R33" t="n">
-        <v>6615084</v>
+        <v>6615036</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3998,9 +4008,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4015,19 +4035,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120238171</v>
+        <v>120237190</v>
       </c>
       <c r="B34" t="n">
         <v>57336</v>
@@ -4063,7 +4083,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4072,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676863</v>
+        <v>677006</v>
       </c>
       <c r="R34" t="n">
-        <v>6615036</v>
+        <v>6614978</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4105,19 +4125,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4132,22 +4142,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120237872</v>
+        <v>120238186</v>
       </c>
       <c r="B35" t="n">
-        <v>57336</v>
+        <v>5189</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4156,20 +4166,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4178,21 +4188,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>677009</v>
+        <v>677003</v>
       </c>
       <c r="R35" t="n">
-        <v>6615043</v>
+        <v>6615007</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4251,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120237190</v>
+        <v>120237736</v>
       </c>
       <c r="B36" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4263,20 +4268,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4285,21 +4290,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>677006</v>
+        <v>676936</v>
       </c>
       <c r="R36" t="n">
-        <v>6614978</v>
+        <v>6615059</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120398837</v>
+        <v>120398695</v>
       </c>
       <c r="B37" t="n">
-        <v>91881</v>
+        <v>90545</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4370,25 +4370,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676918</v>
+        <v>676856</v>
       </c>
       <c r="R37" t="n">
-        <v>6615032</v>
+        <v>6614998</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4448,26 +4448,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120399252</v>
+        <v>120398837</v>
       </c>
       <c r="B38" t="n">
-        <v>57336</v>
+        <v>91881</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4480,42 +4476,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>677049</v>
+        <v>676918</v>
       </c>
       <c r="R38" t="n">
-        <v>6615010</v>
+        <v>6615032</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4578,10 +4566,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120399210</v>
+        <v>120399252</v>
       </c>
       <c r="B39" t="n">
-        <v>8432</v>
+        <v>57336</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4590,34 +4578,33 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4627,10 +4614,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>677015</v>
+        <v>677049</v>
       </c>
       <c r="R39" t="n">
-        <v>6615092</v>
+        <v>6615010</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4671,7 +4658,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4694,10 +4680,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120399303</v>
+        <v>120398946</v>
       </c>
       <c r="B40" t="n">
-        <v>100194</v>
+        <v>90934</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4706,25 +4692,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>1506</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4734,10 +4720,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>677012</v>
+        <v>676919</v>
       </c>
       <c r="R40" t="n">
-        <v>6614962</v>
+        <v>6615041</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4906,10 +4892,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120398811</v>
+        <v>120399210</v>
       </c>
       <c r="B42" t="n">
-        <v>91881</v>
+        <v>8432</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4918,38 +4904,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>676903</v>
+        <v>677015</v>
       </c>
       <c r="R42" t="n">
-        <v>6615027</v>
+        <v>6615092</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4990,6 +4985,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5012,10 +5008,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120399258</v>
+        <v>120398811</v>
       </c>
       <c r="B43" t="n">
-        <v>8432</v>
+        <v>91881</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5024,47 +5020,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>677042</v>
+        <v>676903</v>
       </c>
       <c r="R43" t="n">
-        <v>6614994</v>
+        <v>6615027</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5105,7 +5092,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5128,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120398695</v>
+        <v>120399303</v>
       </c>
       <c r="B44" t="n">
-        <v>90545</v>
+        <v>100194</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5144,21 +5130,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5168,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>676856</v>
+        <v>677012</v>
       </c>
       <c r="R44" t="n">
-        <v>6614998</v>
+        <v>6614962</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5218,22 +5204,26 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120399238</v>
+        <v>120399258</v>
       </c>
       <c r="B45" t="n">
-        <v>8421</v>
+        <v>8432</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5246,21 +5236,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5269,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>677043</v>
+        <v>677042</v>
       </c>
       <c r="R45" t="n">
-        <v>6615044</v>
+        <v>6614994</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,10 +5336,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120398946</v>
+        <v>120399238</v>
       </c>
       <c r="B46" t="n">
-        <v>90934</v>
+        <v>8421</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5358,38 +5348,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1506</v>
+        <v>106554</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>676919</v>
+        <v>677043</v>
       </c>
       <c r="R46" t="n">
-        <v>6615041</v>
+        <v>6615044</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5430,6 +5429,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -2997,10 +2997,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120237246</v>
+        <v>120236814</v>
       </c>
       <c r="B24" t="n">
-        <v>5189</v>
+        <v>90092</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3013,21 +3013,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>5741</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3037,10 +3037,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>677001</v>
+        <v>676879</v>
       </c>
       <c r="R24" t="n">
-        <v>6614969</v>
+        <v>6615084</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,10 +3099,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120236814</v>
+        <v>120237246</v>
       </c>
       <c r="B25" t="n">
-        <v>90092</v>
+        <v>5189</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3115,21 +3115,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5741</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676879</v>
+        <v>677001</v>
       </c>
       <c r="R25" t="n">
-        <v>6615084</v>
+        <v>6614969</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120398946</v>
+        <v>120399210</v>
       </c>
       <c r="B40" t="n">
-        <v>90934</v>
+        <v>8432</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4692,38 +4692,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1506</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676919</v>
+        <v>677015</v>
       </c>
       <c r="R40" t="n">
-        <v>6615041</v>
+        <v>6615092</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4764,6 +4773,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4892,10 +4902,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120399210</v>
+        <v>120398946</v>
       </c>
       <c r="B42" t="n">
-        <v>8432</v>
+        <v>90934</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4904,47 +4914,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>1506</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>677015</v>
+        <v>676919</v>
       </c>
       <c r="R42" t="n">
-        <v>6615092</v>
+        <v>6615041</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4985,7 +4986,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42922-2023 artfynd.xlsx
+++ b/artfynd/A 42922-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112496341</v>
+        <v>120398946</v>
       </c>
       <c r="B2" t="n">
-        <v>99106</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1506</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S Långmyran, Vallentuna, Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676941</v>
+        <v>676919</v>
       </c>
       <c r="R2" t="n">
-        <v>6615022</v>
+        <v>6615041</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Utspridd över stora ytor.</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,34 +754,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>112496352</v>
       </c>
       <c r="B3" t="n">
-        <v>89439</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,41 +877,40 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112496502</v>
+        <v>112496373</v>
       </c>
       <c r="B4" t="n">
-        <v>90945</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -936,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676889</v>
+        <v>676913</v>
       </c>
       <c r="R4" t="n">
-        <v>6615084</v>
+        <v>6615020</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -999,56 +982,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112496262</v>
+        <v>112757820</v>
       </c>
       <c r="B5" t="n">
-        <v>89679</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>S Långmyran, Vallentuna, Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676919</v>
+        <v>676912</v>
       </c>
       <c r="R5" t="n">
-        <v>6615056</v>
+        <v>6614983</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,12 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,34 +1062,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112496373</v>
+        <v>112758282</v>
       </c>
       <c r="B6" t="n">
-        <v>89439</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,26 +1109,20 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>S Långmyran, Vallentuna, Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676912</v>
+        <v>676876</v>
       </c>
       <c r="R6" t="n">
-        <v>6615020</v>
+        <v>6615095</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,12 +1146,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,34 +1160,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112496295</v>
+        <v>112780799</v>
       </c>
       <c r="B7" t="n">
-        <v>103912</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,49 +1189,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>S Långmyran, Vallentuna, Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676929</v>
+        <v>676872</v>
       </c>
       <c r="R7" t="n">
-        <v>6615027</v>
+        <v>6615071</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,12 +1244,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,34 +1258,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112496423</v>
+        <v>112781496</v>
       </c>
       <c r="B8" t="n">
-        <v>90943</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,40 +1287,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>S Långmyran, Vallentuna, Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676938</v>
+        <v>676916</v>
       </c>
       <c r="R8" t="n">
-        <v>6614992</v>
+        <v>6614979</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,12 +1342,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,81 +1356,67 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112496448</v>
+        <v>112781172</v>
       </c>
       <c r="B9" t="n">
-        <v>4764</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>S Långmyran, Vallentuna, Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676928</v>
+        <v>677013</v>
       </c>
       <c r="R9" t="n">
-        <v>6615040</v>
+        <v>6614953</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1515,12 +1440,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,34 +1454,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112757820</v>
+        <v>120236998</v>
       </c>
       <c r="B10" t="n">
-        <v>89677</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,35 +1483,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långmyran (Långmyran), Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676912</v>
+        <v>676961</v>
       </c>
       <c r="R10" t="n">
-        <v>6614983</v>
+        <v>6615062</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,12 +1537,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,27 +1557,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112759613</v>
+        <v>120238457</v>
       </c>
       <c r="B11" t="n">
-        <v>104187</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,35 +1580,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyran (Långmyran), Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>676875</v>
+        <v>676849</v>
       </c>
       <c r="R11" t="n">
-        <v>6615100</v>
+        <v>6615004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,12 +1634,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,27 +1664,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112758282</v>
+        <v>120398695</v>
       </c>
       <c r="B12" t="n">
-        <v>89677</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,35 +1687,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3215</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långmyran (Långmyran), Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676875</v>
+        <v>676856</v>
       </c>
       <c r="R12" t="n">
-        <v>6615095</v>
+        <v>6614998</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,12 +1741,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,15 +1773,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112757642</v>
+        <v>120399055</v>
       </c>
       <c r="B13" t="n">
-        <v>99381</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,35 +1784,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyran (Långmyran), Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676934</v>
+        <v>676930</v>
       </c>
       <c r="R13" t="n">
-        <v>6614968</v>
+        <v>6615106</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,12 +1838,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1948,63 +1858,61 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112780799</v>
+        <v>120236814</v>
       </c>
       <c r="B14" t="n">
-        <v>89677</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>5741</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långmyran (Långmyran), Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676873</v>
+        <v>676879</v>
       </c>
       <c r="R14" t="n">
-        <v>6615072</v>
+        <v>6615084</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,12 +1939,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,27 +1959,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112781172</v>
+        <v>112496423</v>
       </c>
       <c r="B15" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2079,38 +1982,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långmyran (Långmyran), Upl</t>
+          <t>S Långmyran, Vallentuna, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>677013</v>
+        <v>676938</v>
       </c>
       <c r="R15" t="n">
-        <v>6614953</v>
+        <v>6614993</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2134,12 +2039,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,69 +2053,65 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112781989</v>
+        <v>112781095</v>
       </c>
       <c r="B16" t="n">
-        <v>99381</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långmyran (Långmyran), Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>677019</v>
+        <v>676896</v>
       </c>
       <c r="R16" t="n">
-        <v>6614941</v>
+        <v>6615050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,54 +2170,51 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112781496</v>
+        <v>112496502</v>
       </c>
       <c r="B17" t="n">
-        <v>89677</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyran (Långmyran), Upl</t>
+          <t>S Långmyran, Vallentuna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676916</v>
+        <v>676889</v>
       </c>
       <c r="R17" t="n">
-        <v>6614979</v>
+        <v>6615084</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2340,12 +2238,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2354,69 +2252,64 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112781095</v>
+        <v>120398811</v>
       </c>
       <c r="B18" t="n">
-        <v>91183</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyran (Långmyran), Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676896</v>
+        <v>676903</v>
       </c>
       <c r="R18" t="n">
-        <v>6615050</v>
+        <v>6615027</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,12 +2336,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2463,63 +2356,61 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112781211</v>
+        <v>120398837</v>
       </c>
       <c r="B19" t="n">
-        <v>99381</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långmyran (Långmyran), Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>677002</v>
+        <v>676918</v>
       </c>
       <c r="R19" t="n">
-        <v>6614972</v>
+        <v>6615032</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2546,12 +2437,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2566,63 +2457,66 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112780825</v>
+        <v>120237190</v>
       </c>
       <c r="B20" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långmyran (Långmyran), Upl</t>
+          <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676881</v>
+        <v>677006</v>
       </c>
       <c r="R20" t="n">
-        <v>6615076</v>
+        <v>6614978</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2649,12 +2543,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2669,27 +2563,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120237246</v>
+        <v>120237239</v>
       </c>
       <c r="B21" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2697,16 +2586,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2715,13 +2604,18 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>677001</v>
+        <v>677002</v>
       </c>
       <c r="R21" t="n">
         <v>6614969</v>
@@ -2783,15 +2677,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120237606</v>
+        <v>120237707</v>
       </c>
       <c r="B22" t="n">
-        <v>100263</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,34 +2688,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676929</v>
+        <v>676938</v>
       </c>
       <c r="R22" t="n">
-        <v>6614995</v>
+        <v>6615070</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,50 +2779,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120237674</v>
+        <v>120237872</v>
       </c>
       <c r="B23" t="n">
-        <v>90648</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676920</v>
+        <v>677009</v>
       </c>
       <c r="R23" t="n">
-        <v>6615057</v>
+        <v>6615043</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,15 +2881,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120237296</v>
+        <v>120238171</v>
       </c>
       <c r="B24" t="n">
-        <v>100263</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,34 +2892,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>677019</v>
+        <v>676863</v>
       </c>
       <c r="R24" t="n">
-        <v>6614935</v>
+        <v>6615036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3060,9 +2954,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3077,31 +2981,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120238171</v>
+        <v>120399252</v>
       </c>
       <c r="B25" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3123,21 +3022,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676863</v>
+        <v>677049</v>
       </c>
       <c r="R25" t="n">
-        <v>6615036</v>
+        <v>6615010</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3164,22 +3066,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3194,70 +3086,73 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120237707</v>
+        <v>112496448</v>
       </c>
       <c r="B26" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Upl</t>
+          <t>S Långmyran, Vallentuna, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676938</v>
+        <v>676927</v>
       </c>
       <c r="R26" t="n">
-        <v>6615070</v>
+        <v>6615039</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3281,12 +3176,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,33 +3190,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120236814</v>
+        <v>120237441</v>
       </c>
       <c r="B27" t="n">
-        <v>90137</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3329,34 +3220,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5741</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676879</v>
+        <v>677003</v>
       </c>
       <c r="R27" t="n">
-        <v>6615084</v>
+        <v>6615036</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,9 +3282,19 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3403,27 +3309,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120237628</v>
+        <v>120237736</v>
       </c>
       <c r="B28" t="n">
-        <v>100263</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3431,21 +3332,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3455,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676920</v>
+        <v>676936</v>
       </c>
       <c r="R28" t="n">
-        <v>6615038</v>
+        <v>6615059</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3517,50 +3418,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120236816</v>
+        <v>120239377</v>
       </c>
       <c r="B29" t="n">
-        <v>100263</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>676881</v>
+        <v>676807</v>
       </c>
       <c r="R29" t="n">
-        <v>6615082</v>
+        <v>6615027</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,15 +3524,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120236998</v>
+        <v>120236974</v>
       </c>
       <c r="B30" t="n">
-        <v>90595</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3635,21 +3535,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3659,10 +3559,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676961</v>
+        <v>676946</v>
       </c>
       <c r="R30" t="n">
-        <v>6615062</v>
+        <v>6615094</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,15 +3621,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120238186</v>
+        <v>120237246</v>
       </c>
       <c r="B31" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3761,10 +3656,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>677003</v>
+        <v>677001</v>
       </c>
       <c r="R31" t="n">
-        <v>6615007</v>
+        <v>6614969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,15 +3718,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120238457</v>
+        <v>120238186</v>
       </c>
       <c r="B32" t="n">
-        <v>90595</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3839,21 +3729,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3863,10 +3753,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676849</v>
+        <v>677003</v>
       </c>
       <c r="R32" t="n">
-        <v>6615004</v>
+        <v>6615007</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3896,19 +3786,9 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3923,44 +3803,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120237190</v>
+        <v>120399806</v>
       </c>
       <c r="B33" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3969,21 +3844,25 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>677006</v>
+        <v>676952</v>
       </c>
       <c r="R33" t="n">
-        <v>6614978</v>
+        <v>6615123</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4010,12 +3889,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4024,6 +3903,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4038,19 +3918,18 @@
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120237736</v>
+        <v>120237776</v>
       </c>
       <c r="B34" t="n">
-        <v>57701</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4058,21 +3937,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4082,10 +3961,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676936</v>
+        <v>676944</v>
       </c>
       <c r="R34" t="n">
-        <v>6615059</v>
+        <v>6615120</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4144,55 +4023,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120237872</v>
+        <v>120399210</v>
       </c>
       <c r="B35" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>677009</v>
+        <v>677015</v>
       </c>
       <c r="R35" t="n">
-        <v>6615043</v>
+        <v>6615092</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4219,12 +4097,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4233,6 +4111,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4247,59 +4126,62 @@
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120237239</v>
+        <v>120399258</v>
       </c>
       <c r="B36" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>677002</v>
+        <v>677042</v>
       </c>
       <c r="R36" t="n">
-        <v>6614969</v>
+        <v>6614994</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4326,12 +4208,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4340,6 +4222,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4354,49 +4237,49 @@
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120399252</v>
+        <v>120399238</v>
       </c>
       <c r="B37" t="n">
-        <v>57351</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4406,10 +4289,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>677049</v>
+        <v>677043</v>
       </c>
       <c r="R37" t="n">
-        <v>6615010</v>
+        <v>6615044</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4450,6 +4333,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4472,53 +4356,60 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120398811</v>
+        <v>112496295</v>
       </c>
       <c r="B38" t="n">
-        <v>91954</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Upl</t>
+          <t>S Långmyran, Vallentuna, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676903</v>
+        <v>676929</v>
       </c>
       <c r="R38" t="n">
         <v>6615027</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4542,12 +4433,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4556,37 +4447,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120399303</v>
+        <v>112759613</v>
       </c>
       <c r="B39" t="n">
-        <v>100280</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4594,34 +4477,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>677012</v>
+        <v>676875</v>
       </c>
       <c r="R39" t="n">
-        <v>6614962</v>
+        <v>6615100</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4648,12 +4532,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4668,69 +4552,64 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120398837</v>
+        <v>112496341</v>
       </c>
       <c r="B40" t="n">
-        <v>91954</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Upl</t>
+          <t>S Långmyran, Vallentuna, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676918</v>
+        <v>676941</v>
       </c>
       <c r="R40" t="n">
-        <v>6615032</v>
+        <v>6615023</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4754,12 +4633,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Utspridd över stora ytor.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4768,37 +4652,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120399210</v>
+        <v>112757642</v>
       </c>
       <c r="B41" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4806,43 +4682,35 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>677015</v>
+        <v>676933</v>
       </c>
       <c r="R41" t="n">
-        <v>6615092</v>
+        <v>6614968</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4869,12 +4737,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4883,38 +4751,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120399238</v>
+        <v>112781211</v>
       </c>
       <c r="B42" t="n">
-        <v>8421</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4922,43 +4780,35 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>677043</v>
+        <v>677002</v>
       </c>
       <c r="R42" t="n">
-        <v>6615044</v>
+        <v>6614973</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4985,12 +4835,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4999,38 +4849,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120399055</v>
+        <v>112781989</v>
       </c>
       <c r="B43" t="n">
-        <v>90609</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5038,34 +4878,35 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>676930</v>
+        <v>677019</v>
       </c>
       <c r="R43" t="n">
-        <v>6615106</v>
+        <v>6614941</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5092,12 +4933,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5112,31 +4953,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120399258</v>
+        <v>120236816</v>
       </c>
       <c r="B44" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5144,43 +4976,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>677042</v>
+        <v>676881</v>
       </c>
       <c r="R44" t="n">
-        <v>6614994</v>
+        <v>6615082</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,12 +5030,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5221,7 +5044,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5236,23 +5058,14 @@
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120398695</v>
+        <v>120237296</v>
       </c>
       <c r="B45" t="n">
-        <v>90609</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5260,21 +5073,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5284,10 +5097,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676856</v>
+        <v>677019</v>
       </c>
       <c r="R45" t="n">
-        <v>6614998</v>
+        <v>6614935</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,12 +5127,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5334,49 +5147,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120398946</v>
+        <v>120237606</v>
       </c>
       <c r="B46" t="n">
-        <v>91002</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1506</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>676919</v>
+        <v>676929</v>
       </c>
       <c r="R46" t="n">
-        <v>6615041</v>
+        <v>6614995</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5416,12 +5224,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5444,7 +5252,201 @@
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr">
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120237628</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>676920</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6615038</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120399303</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>677012</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6614962</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Frösunda</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
         <is>
           <t>Vallentuna skogsgrupp</t>
         </is>
